--- a/TabeleExcel/Tabele_Id/Salary_history.xlsx
+++ b/TabeleExcel/Tabele_Id/Salary_history.xlsx
@@ -123,11 +123,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -498,7 +498,7 @@
         <v>10000</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>42024</v>
+        <v>41294</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -573,7 +573,7 @@
         <v>3800</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>43840</v>
+        <v>43475</v>
       </c>
       <c r="E16" s="1"/>
     </row>

--- a/TabeleExcel/Tabele_Id/Salary_history.xlsx
+++ b/TabeleExcel/Tabele_Id/Salary_history.xlsx
@@ -690,7 +690,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>5300</v>
+        <v>4500</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>44722</v>
